--- a/rag/excel/matrix_cohen.xlsx
+++ b/rag/excel/matrix_cohen.xlsx
@@ -1369,7 +1369,6 @@
       <c r="J11" t="n">
         <v>31</v>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
         <v>0.7519998311488212</v>
       </c>
@@ -1458,7 +1457,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1473,16 +1472,16 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5636505211037015</v>
+        <v>0.6898891937747429</v>
       </c>
     </row>
     <row r="3">
@@ -1495,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1519,10 +1518,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5636505211037015</v>
+        <v>0.6898891937747429</v>
       </c>
     </row>
     <row r="4">
@@ -1532,13 +1531,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1559,10 +1558,10 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5636505211037015</v>
+        <v>0.6898891937747429</v>
       </c>
     </row>
     <row r="5">
@@ -1572,7 +1571,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -1599,10 +1598,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5636505211037015</v>
+        <v>0.6898891937747429</v>
       </c>
     </row>
     <row r="6">
@@ -1612,10 +1611,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1624,10 +1623,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1639,10 +1638,10 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5636505211037015</v>
+        <v>0.6898891937747429</v>
       </c>
     </row>
     <row r="7">
@@ -1652,7 +1651,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -1667,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1676,13 +1675,13 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>21</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5636505211037015</v>
+        <v>0.6898891937747429</v>
       </c>
     </row>
     <row r="8">
@@ -1695,10 +1694,10 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1707,10 +1706,10 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -1719,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5636505211037015</v>
+        <v>0.6898891937747429</v>
       </c>
     </row>
     <row r="9">
@@ -1732,37 +1731,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I9" t="n">
+        <v>14</v>
+      </c>
+      <c r="J9" t="n">
         <v>12</v>
       </c>
-      <c r="J9" t="n">
-        <v>11</v>
-      </c>
       <c r="K9" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5636505211037015</v>
+        <v>0.6898891937747429</v>
       </c>
     </row>
     <row r="10">
@@ -1772,7 +1771,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -1796,13 +1795,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K10" t="n">
         <v>23</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5636505211037015</v>
+        <v>0.6898891937747429</v>
       </c>
     </row>
     <row r="11">
@@ -1812,34 +1811,35 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D11" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H11" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>32</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>0.5636505211037015</v>
+        <v>0.6898891937747429</v>
       </c>
     </row>
   </sheetData>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1938,7 +1938,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -1950,7 +1950,7 @@
         <v>23</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7128168390889362</v>
+        <v>0.7230872822153017</v>
       </c>
     </row>
     <row r="3">
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
         <v>26</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7128168390889362</v>
+        <v>0.7230872822153017</v>
       </c>
     </row>
     <row r="4">
@@ -2000,13 +2000,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2030,7 +2030,7 @@
         <v>51</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7128168390889362</v>
+        <v>0.7230872822153017</v>
       </c>
     </row>
     <row r="5">
@@ -2070,7 +2070,7 @@
         <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7128168390889362</v>
+        <v>0.7230872822153017</v>
       </c>
     </row>
     <row r="6">
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -2092,25 +2092,25 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7128168390889362</v>
+        <v>0.7230872822153017</v>
       </c>
     </row>
     <row r="7">
@@ -2123,7 +2123,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -2135,7 +2135,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -2150,7 +2150,7 @@
         <v>21</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7128168390889362</v>
+        <v>0.7230872822153017</v>
       </c>
     </row>
     <row r="8">
@@ -2166,7 +2166,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2175,10 +2175,10 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -2190,7 +2190,7 @@
         <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7128168390889362</v>
+        <v>0.7230872822153017</v>
       </c>
     </row>
     <row r="9">
@@ -2200,37 +2200,37 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>9</v>
       </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>11</v>
-      </c>
       <c r="I9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
         <v>46</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7128168390889362</v>
+        <v>0.7230872822153017</v>
       </c>
     </row>
     <row r="10">
@@ -2258,19 +2258,19 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
         <v>23</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7128168390889362</v>
+        <v>0.7230872822153017</v>
       </c>
     </row>
     <row r="11">
@@ -2280,34 +2280,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H11" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7128168390889362</v>
+        <v>0.7230872822153017</v>
       </c>
     </row>
   </sheetData>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -2883,10 +2883,10 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6367390153520383</v>
+        <v>0.6159804753820034</v>
       </c>
     </row>
     <row r="3">
@@ -2902,7 +2902,7 @@
         <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2917,7 +2917,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2926,7 +2926,7 @@
         <v>26</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6367390153520383</v>
+        <v>0.6159804753820034</v>
       </c>
     </row>
     <row r="4">
@@ -2936,13 +2936,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2957,7 +2957,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -2966,7 +2966,7 @@
         <v>51</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6367390153520383</v>
+        <v>0.6159804753820034</v>
       </c>
     </row>
     <row r="5">
@@ -3006,7 +3006,7 @@
         <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6367390153520383</v>
+        <v>0.6159804753820034</v>
       </c>
     </row>
     <row r="6">
@@ -3016,13 +3016,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3031,13 +3031,13 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -3046,7 +3046,7 @@
         <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6367390153520383</v>
+        <v>0.6159804753820034</v>
       </c>
     </row>
     <row r="7">
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3068,10 +3068,10 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -3086,7 +3086,7 @@
         <v>21</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6367390153520383</v>
+        <v>0.6159804753820034</v>
       </c>
     </row>
     <row r="8">
@@ -3099,10 +3099,10 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -3126,7 +3126,7 @@
         <v>32</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6367390153520383</v>
+        <v>0.6159804753820034</v>
       </c>
     </row>
     <row r="9">
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -3148,25 +3148,25 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
         <v>29</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>46</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6367390153520383</v>
+        <v>0.6159804753820034</v>
       </c>
     </row>
     <row r="10">
@@ -3179,16 +3179,16 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -3197,16 +3197,16 @@
         <v>4</v>
       </c>
       <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="n">
         <v>4</v>
       </c>
-      <c r="J10" t="n">
-        <v>5</v>
-      </c>
       <c r="K10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6367390153520383</v>
+        <v>0.6159804753820034</v>
       </c>
     </row>
     <row r="11">
@@ -3216,13 +3216,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D11" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -3231,19 +3231,19 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H11" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6367390153520383</v>
+        <v>0.6159804753820034</v>
       </c>
     </row>
   </sheetData>

--- a/rag/excel/matrix_cohen.xlsx
+++ b/rag/excel/matrix_cohen.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="mistral_Rag" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="phi4_Rag" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="llama3.3_Rag" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -506,13 +508,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -527,16 +529,16 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01269444595353217</v>
+        <v>0.6007051377354883</v>
       </c>
     </row>
     <row r="3">
@@ -546,13 +548,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -573,10 +575,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01269444595353217</v>
+        <v>0.6007051377354883</v>
       </c>
     </row>
     <row r="4">
@@ -586,13 +588,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -613,10 +615,10 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01269444595353217</v>
+        <v>0.6007051377354883</v>
       </c>
     </row>
     <row r="5">
@@ -626,7 +628,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -635,7 +637,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -653,10 +655,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01269444595353217</v>
+        <v>0.6007051377354883</v>
       </c>
     </row>
     <row r="6">
@@ -666,13 +668,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -684,19 +686,19 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01269444595353217</v>
+        <v>0.6007051377354883</v>
       </c>
     </row>
     <row r="7">
@@ -706,7 +708,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -721,22 +723,22 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01269444595353217</v>
+        <v>0.6007051377354883</v>
       </c>
     </row>
     <row r="8">
@@ -749,10 +751,10 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -761,10 +763,10 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -773,10 +775,10 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01269444595353217</v>
+        <v>0.6007051377354883</v>
       </c>
     </row>
     <row r="9">
@@ -786,7 +788,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -801,22 +803,22 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01269444595353217</v>
+        <v>0.6007051377354883</v>
       </c>
     </row>
     <row r="10">
@@ -826,13 +828,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -844,19 +846,19 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01269444595353217</v>
+        <v>0.6007051377354883</v>
       </c>
     </row>
     <row r="11">
@@ -866,35 +868,971 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6007051377354883</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>SumRow</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>kappa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>22</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6996710733066561</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>26</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6996710733066561</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>49</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>51</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.6996710733066561</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.6996710733066561</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.6996710733066561</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>17</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>21</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.6996710733066561</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>29</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>34</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.6996710733066561</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>12</v>
+      </c>
+      <c r="J9" t="n">
+        <v>15</v>
+      </c>
+      <c r="K9" t="n">
+        <v>46</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.6996710733066561</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>21</v>
+      </c>
+      <c r="K10" t="n">
+        <v>23</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.6996710733066561</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SumCol</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>27</v>
+      </c>
+      <c r="C11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D11" t="n">
+        <v>55</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>24</v>
+      </c>
+      <c r="H11" t="n">
+        <v>39</v>
+      </c>
+      <c r="I11" t="n">
+        <v>13</v>
+      </c>
+      <c r="J11" t="n">
+        <v>39</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6996710733066561</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>SumRow</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>kappa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>23</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.727521872035417</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>26</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.727521872035417</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>49</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>51</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.727521872035417</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.727521872035417</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.727521872035417</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>21</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.727521872035417</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>31</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>34</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.727521872035417</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n">
+        <v>18</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>46</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.727521872035417</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20</v>
+      </c>
+      <c r="K10" t="n">
+        <v>23</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.727521872035417</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SumCol</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>33</v>
+      </c>
+      <c r="C11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D11" t="n">
+        <v>52</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>18</v>
+      </c>
+      <c r="H11" t="n">
+        <v>46</v>
+      </c>
+      <c r="I11" t="n">
+        <v>21</v>
+      </c>
+      <c r="J11" t="n">
+        <v>32</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>0.01269444595353217</v>
+        <v>0.727521872035417</v>
       </c>
     </row>
   </sheetData>

--- a/rag/excel/matrix_cohen.xlsx
+++ b/rag/excel/matrix_cohen.xlsx
@@ -508,13 +508,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -529,16 +529,16 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6007051377354883</v>
+        <v>0.00423728813559322</v>
       </c>
     </row>
     <row r="3">
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -575,10 +575,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6007051377354883</v>
+        <v>0.00423728813559322</v>
       </c>
     </row>
     <row r="4">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -615,10 +615,10 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6007051377354883</v>
+        <v>0.00423728813559322</v>
       </c>
     </row>
     <row r="5">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -637,7 +637,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -655,10 +655,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6007051377354883</v>
+        <v>0.00423728813559322</v>
       </c>
     </row>
     <row r="6">
@@ -668,13 +668,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -686,19 +686,19 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6007051377354883</v>
+        <v>0.00423728813559322</v>
       </c>
     </row>
     <row r="7">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -723,22 +723,22 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6007051377354883</v>
+        <v>0.00423728813559322</v>
       </c>
     </row>
     <row r="8">
@@ -751,10 +751,10 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -763,10 +763,10 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -775,10 +775,10 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6007051377354883</v>
+        <v>0.00423728813559322</v>
       </c>
     </row>
     <row r="9">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -803,22 +803,22 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6007051377354883</v>
+        <v>0.00423728813559322</v>
       </c>
     </row>
     <row r="10">
@@ -828,13 +828,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -846,19 +846,19 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6007051377354883</v>
+        <v>0.00423728813559322</v>
       </c>
     </row>
     <row r="11">
@@ -868,34 +868,35 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>6</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>0.6007051377354883</v>
+        <v>0.00423728813559322</v>
       </c>
     </row>
   </sheetData>
@@ -1830,7 +1831,6 @@
       <c r="J11" t="n">
         <v>32</v>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
         <v>0.727521872035417</v>
       </c>

--- a/rag/excel/matrix_cohen.xlsx
+++ b/rag/excel/matrix_cohen.xlsx
@@ -508,13 +508,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -529,16 +529,16 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00423728813559322</v>
+        <v>0.6129726990561856</v>
       </c>
     </row>
     <row r="3">
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -575,10 +575,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00423728813559322</v>
+        <v>0.6129726990561856</v>
       </c>
     </row>
     <row r="4">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -615,10 +615,10 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00423728813559322</v>
+        <v>0.6129726990561856</v>
       </c>
     </row>
     <row r="5">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -637,7 +637,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -655,10 +655,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00423728813559322</v>
+        <v>0.6129726990561856</v>
       </c>
     </row>
     <row r="6">
@@ -668,13 +668,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -683,22 +683,22 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00423728813559322</v>
+        <v>0.6129726990561856</v>
       </c>
     </row>
     <row r="7">
@@ -708,37 +708,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00423728813559322</v>
+        <v>0.6129726990561856</v>
       </c>
     </row>
     <row r="8">
@@ -748,13 +748,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -775,10 +775,10 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00423728813559322</v>
+        <v>0.6129726990561856</v>
       </c>
     </row>
     <row r="9">
@@ -788,37 +788,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00423728813559322</v>
+        <v>0.6129726990561856</v>
       </c>
     </row>
     <row r="10">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -846,19 +846,19 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00423728813559322</v>
+        <v>0.6129726990561856</v>
       </c>
     </row>
     <row r="11">
@@ -868,35 +868,35 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>0.00423728813559322</v>
+        <v>0.6129726990561856</v>
       </c>
     </row>
   </sheetData>

--- a/rag/excel/matrix_cohen.xlsx
+++ b/rag/excel/matrix_cohen.xlsx
@@ -12,6 +12,7 @@
     <sheet name="phi4_Rag_keyword" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="llama3.3_Rag_keyword" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="llama3.3_Rag" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Rag_phi4_rag" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1856,6 +1857,475 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="I1" s="8" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="K1" s="8" t="inlineStr">
+        <is>
+          <t>SumRow</t>
+        </is>
+      </c>
+      <c r="L1" s="8" t="inlineStr">
+        <is>
+          <t>kappa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>23</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.7855657414480944</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>26</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.7855657414480944</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>51</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.7855657414480944</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.7855657414480944</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.7855657414480944</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>17</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>21</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.7855657414480944</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>34</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.7855657414480944</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>29</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K9" t="n">
+        <v>46</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.7855657414480944</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>23</v>
+      </c>
+      <c r="K10" t="n">
+        <v>23</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.7855657414480944</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>SumCol</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D11" t="n">
+        <v>58</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" t="n">
+        <v>33</v>
+      </c>
+      <c r="I11" t="n">
+        <v>33</v>
+      </c>
+      <c r="J11" t="n">
+        <v>35</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0.7855657414480944</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -8733,37 +9203,37 @@
           <t>MonCal.Interpret</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="C2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="0" t="n">
         <v>0.7018864836109179</v>
       </c>
     </row>
@@ -8773,37 +9243,37 @@
           <t>MonCal.Facts.RF</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
+      <c r="B3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
+      <c r="D3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="0" t="n">
         <v>0.7018864836109179</v>
       </c>
     </row>
@@ -8813,37 +9283,37 @@
           <t>MonCal.Facts.DC</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="B4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="0" t="n">
         <v>48</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="E4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="0" t="n">
         <v>0.7018864836109179</v>
       </c>
     </row>
@@ -8853,37 +9323,37 @@
           <t>BDS.Emotions</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="B5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="F5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="0" t="n">
         <v>0.7018864836109179</v>
       </c>
     </row>
@@ -8893,37 +9363,37 @@
           <t>MotOrient.Value</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="B6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
+      <c r="G6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="0" t="n">
         <v>0.7018864836109179</v>
       </c>
     </row>
@@ -8933,37 +9403,37 @@
           <t>MotOrient.SelfEff</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="C7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="H7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="0" t="n">
         <v>0.7018864836109179</v>
       </c>
     </row>
@@ -8973,37 +9443,37 @@
           <t>DomKldg</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="B8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="I8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="0" t="n">
         <v>32</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="0" t="n">
         <v>0.7018864836109179</v>
       </c>
     </row>
@@ -9013,37 +9483,37 @@
           <t>StratKldg</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="B9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="0" t="n">
         <v>22</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="J9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="0" t="n">
         <v>33</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="0" t="n">
         <v>0.7018864836109179</v>
       </c>
     </row>
@@ -9053,37 +9523,37 @@
           <t>CTRL</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
+      <c r="B10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
+      <c r="I10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="0" t="n">
         <v>0.7018864836109179</v>
       </c>
     </row>
@@ -9093,35 +9563,35 @@
           <t>SumCol</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="0" t="n">
         <v>26</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="0" t="n">
         <v>26</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="0" t="n">
         <v>49</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="0" t="n">
         <v>45</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="0" t="n">
         <v>24</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
+      <c r="K11" s="0" t="inlineStr"/>
+      <c r="L11" s="0" t="n">
         <v>0.7018864836109179</v>
       </c>
     </row>

--- a/rag/excel/matrix_cohen.xlsx
+++ b/rag/excel/matrix_cohen.xlsx
@@ -1939,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1948,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -1963,7 +1963,7 @@
         <v>23</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7855657414480944</v>
+        <v>0.7760862200389599</v>
       </c>
     </row>
     <row r="3">
@@ -2003,7 +2003,7 @@
         <v>26</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7855657414480944</v>
+        <v>0.7760862200389599</v>
       </c>
     </row>
     <row r="4">
@@ -2043,7 +2043,7 @@
         <v>51</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7855657414480944</v>
+        <v>0.7760862200389599</v>
       </c>
     </row>
     <row r="5">
@@ -2083,7 +2083,7 @@
         <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7855657414480944</v>
+        <v>0.7760862200389599</v>
       </c>
     </row>
     <row r="6">
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -2114,16 +2114,16 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7855657414480944</v>
+        <v>0.7760862200389599</v>
       </c>
     </row>
     <row r="7">
@@ -2133,13 +2133,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -2157,13 +2157,13 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>21</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7855657414480944</v>
+        <v>0.7760862200389599</v>
       </c>
     </row>
     <row r="8">
@@ -2191,10 +2191,10 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
@@ -2203,7 +2203,7 @@
         <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7855657414480944</v>
+        <v>0.7760862200389599</v>
       </c>
     </row>
     <row r="9">
@@ -2213,14 +2213,14 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
         <v>2</v>
       </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
@@ -2231,19 +2231,19 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>25</v>
+      </c>
+      <c r="J9" t="n">
         <v>7</v>
-      </c>
-      <c r="I9" t="n">
-        <v>29</v>
-      </c>
-      <c r="J9" t="n">
-        <v>6</v>
       </c>
       <c r="K9" t="n">
         <v>46</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7855657414480944</v>
+        <v>0.7760862200389599</v>
       </c>
     </row>
     <row r="10">
@@ -2283,7 +2283,7 @@
         <v>23</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7855657414480944</v>
+        <v>0.7760862200389599</v>
       </c>
     </row>
     <row r="11">
@@ -2293,13 +2293,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D11" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
@@ -2311,17 +2311,17 @@
         <v>20</v>
       </c>
       <c r="H11" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I11" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>0.7855657414480944</v>
+        <v>0.7760862200389599</v>
       </c>
     </row>
   </sheetData>
